--- a/Data/Point.xlsx
+++ b/Data/Point.xlsx
@@ -1,34 +1,74 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99735EC-8F03-4A67-94C6-9484E9699A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="6540" yWindow="2925" windowWidth="25935" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Point" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Point" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+  <si>
+    <t>ItemId</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>ShowInWallet</t>
+  </si>
+  <si>
+    <t>SortOrder</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Dia</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +87,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,91 +389,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col min="1" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ItemId</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ShowInWallet</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>SortOrder</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>900001</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>900002</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Dia</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>20</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Data/Point.xlsx
+++ b/Data/Point.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99735EC-8F03-4A67-94C6-9484E9699A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93523B7-346A-4E1B-91F4-02B44A04F6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="2925" windowWidth="25935" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="55095" yWindow="2175" windowWidth="14940" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>ItemId</t>
   </si>
@@ -28,9 +28,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>ShowInWallet</t>
   </si>
   <si>
@@ -43,7 +40,23 @@
     <t>Dia</t>
   </si>
   <si>
-    <t>Diamond</t>
+    <t>BlackEssence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoyalCoin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MagicShard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mileage</t>
   </si>
 </sst>
 </file>
@@ -390,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="16" customWidth="1"/>
+    <col min="1" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -409,42 +422,103 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>20</v>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1999</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Point.xlsx
+++ b/Data/Point.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93523B7-346A-4E1B-91F4-02B44A04F6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FE6933-DA3E-4B4D-8D2E-E893F3BFDB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="55095" yWindow="2175" windowWidth="14940" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5160" yWindow="3480" windowWidth="25920" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>ItemId</t>
   </si>
@@ -57,6 +57,10 @@
   </si>
   <si>
     <t>Mileage</t>
+  </si>
+  <si>
+    <t>Starforce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -403,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -509,16 +513,30 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1999</v>
+        <v>1007</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
         <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1999</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Point.xlsx
+++ b/Data/Point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FE6933-DA3E-4B4D-8D2E-E893F3BFDB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CA218C-3935-4CFC-BB87-B5723EA36198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5160" yWindow="3480" windowWidth="25920" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>ItemId</t>
   </si>
@@ -60,6 +60,14 @@
   </si>
   <si>
     <t>Starforce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponSummon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LanternSummon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -407,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -527,16 +535,44 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1999</v>
+        <v>1008</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
         <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1999</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Point.xlsx
+++ b/Data/Point.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CA218C-3935-4CFC-BB87-B5723EA36198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE3EC27-665F-4FC7-A617-469E3B8C6DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>ItemId</t>
   </si>
@@ -68,6 +68,26 @@
   </si>
   <si>
     <t>LanternSummon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonWeaponTicket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonExperienceTicket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonEquipmentTicket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonTrainingTicket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonEnhanceTicket</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -415,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -563,16 +583,86 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1999</v>
+        <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
         <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1011</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1012</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1013</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1014</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1999</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Point.xlsx
+++ b/Data/Point.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE3EC27-665F-4FC7-A617-469E3B8C6DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AD80E9-14CD-493B-AEBA-4724EF1E0823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>ItemId</t>
   </si>
@@ -88,6 +88,10 @@
   </si>
   <si>
     <t>DungeonEnhanceTicket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -435,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -457,211 +461,225 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
+        <v>1014</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>1999</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>10</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
         <v>1000</v>
       </c>
     </row>
